--- a/Result/profitability/7732.xlsx
+++ b/Result/profitability/7732.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM15"/>
+  <dimension ref="A1:AM16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2335,6 +2335,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7732</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>233</v>
+      </c>
+      <c r="D16" t="n">
+        <v>179</v>
+      </c>
+      <c r="E16" t="n">
+        <v>54</v>
+      </c>
+      <c r="F16" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3.83%</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4112499999999999</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28.00625</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.6499999999999999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.7926829268292683</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-5.48</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.190608695652174</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-7.109999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.2340355497037525</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
